--- a/data/out/best_models_ml/validation_ml/validation_ml_metrics.xlsx
+++ b/data/out/best_models_ml/validation_ml/validation_ml_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.4333305358886719</v>
+        <v>0.6960635185241699</v>
       </c>
       <c r="I2" t="n">
         <v>48192</v>
@@ -518,19 +518,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-2.291189939668012</v>
+        <v>-0.04015756724581765</v>
       </c>
       <c r="B3" t="n">
-        <v>158.2867711645409</v>
+        <v>28.31853346760366</v>
       </c>
       <c r="C3" t="n">
-        <v>29763.6052745423</v>
+        <v>9689.871787300397</v>
       </c>
       <c r="D3" t="n">
-        <v>172.521318319048</v>
+        <v>98.43714637930336</v>
       </c>
       <c r="E3" t="n">
-        <v>129.2158105365643</v>
+        <v>14.288104873417</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,30 +543,30 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.3488097190856934</v>
+        <v>1.977282762527466</v>
       </c>
       <c r="I3" t="n">
-        <v>48192</v>
+        <v>48168</v>
       </c>
       <c r="J3" t="n">
-        <v>744</v>
+        <v>720</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-1.973054119416432</v>
+        <v>-1.96817166496895</v>
       </c>
       <c r="B4" t="n">
-        <v>150.4228411073595</v>
+        <v>150.2860846723777</v>
       </c>
       <c r="C4" t="n">
-        <v>26886.57017439979</v>
+        <v>26842.41609954854</v>
       </c>
       <c r="D4" t="n">
-        <v>163.9712480113504</v>
+        <v>163.8365530019126</v>
       </c>
       <c r="E4" t="n">
-        <v>122.566287053879</v>
+        <v>122.4497237586304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.4662144184112549</v>
+        <v>0.7009918689727783</v>
       </c>
       <c r="I4" t="n">
         <v>48192</v>
@@ -590,19 +590,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-2.291189939668012</v>
+        <v>-0.0387578269088904</v>
       </c>
       <c r="B5" t="n">
-        <v>158.2867711645409</v>
+        <v>28.51124323958157</v>
       </c>
       <c r="C5" t="n">
-        <v>29763.6052745423</v>
+        <v>9676.83212405375</v>
       </c>
       <c r="D5" t="n">
-        <v>172.521318319048</v>
+        <v>98.37089063363079</v>
       </c>
       <c r="E5" t="n">
-        <v>129.2158105365643</v>
+        <v>14.47584090336464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -615,30 +615,30 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.3678665161132812</v>
+        <v>2.259403467178345</v>
       </c>
       <c r="I5" t="n">
-        <v>48192</v>
+        <v>48168</v>
       </c>
       <c r="J5" t="n">
-        <v>744</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.946920755091728</v>
+        <v>-1.943924026194739</v>
       </c>
       <c r="B6" t="n">
-        <v>149.7445185176173</v>
+        <v>149.2324424543903</v>
       </c>
       <c r="C6" t="n">
-        <v>26650.23524553976</v>
+        <v>26623.13457446339</v>
       </c>
       <c r="D6" t="n">
-        <v>163.2489976861719</v>
+        <v>163.1659724773011</v>
       </c>
       <c r="E6" t="n">
-        <v>122.0203502184764</v>
+        <v>121.5315355356862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.3874731063842773</v>
+        <v>0.5806369781494141</v>
       </c>
       <c r="I6" t="n">
         <v>48192</v>
@@ -662,19 +662,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-2.291189939668012</v>
+        <v>-0.03842206191043696</v>
       </c>
       <c r="B7" t="n">
-        <v>158.2867711645409</v>
+        <v>27.93000571972317</v>
       </c>
       <c r="C7" t="n">
-        <v>29763.6052745423</v>
+        <v>9673.704213544679</v>
       </c>
       <c r="D7" t="n">
-        <v>172.521318319048</v>
+        <v>98.35499079123885</v>
       </c>
       <c r="E7" t="n">
-        <v>129.2158105365643</v>
+        <v>13.96465680109469</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.3802132606506348</v>
+        <v>2.30964732170105</v>
       </c>
       <c r="I7" t="n">
-        <v>48192</v>
+        <v>48168</v>
       </c>
       <c r="J7" t="n">
-        <v>744</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.1558856878930912</v>
+        <v>-0.8770108271611861</v>
       </c>
       <c r="B8" t="n">
-        <v>70.07542677912642</v>
+        <v>106.8890401556758</v>
       </c>
       <c r="C8" t="n">
-        <v>10453.15706100301</v>
+        <v>16974.59289186544</v>
       </c>
       <c r="D8" t="n">
-        <v>102.2406820253221</v>
+        <v>130.2865798609567</v>
       </c>
       <c r="E8" t="n">
-        <v>52.96826787337275</v>
+        <v>84.99624794861123</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>466.8665671348572</v>
+        <v>349.0084295272827</v>
       </c>
       <c r="I8" t="n">
         <v>48192</v>
@@ -734,19 +734,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-2.291189939668012</v>
+        <v>-0.03951827208107406</v>
       </c>
       <c r="B9" t="n">
-        <v>158.2867711645409</v>
+        <v>28.36259104174097</v>
       </c>
       <c r="C9" t="n">
-        <v>29763.6052745423</v>
+        <v>9683.916258661589</v>
       </c>
       <c r="D9" t="n">
-        <v>172.521318319048</v>
+        <v>98.40689131692754</v>
       </c>
       <c r="E9" t="n">
-        <v>129.2158105365643</v>
+        <v>14.33778493989079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -759,30 +759,30 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.4006247520446777</v>
+        <v>1.964268207550049</v>
       </c>
       <c r="I9" t="n">
-        <v>48192</v>
+        <v>48168</v>
       </c>
       <c r="J9" t="n">
-        <v>744</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.05374127875948842</v>
+        <v>0.05192766362374146</v>
       </c>
       <c r="B10" t="n">
-        <v>61.61679096755162</v>
+        <v>57.85008272130002</v>
       </c>
       <c r="C10" t="n">
-        <v>9529.422505968314</v>
+        <v>8573.81412464528</v>
       </c>
       <c r="D10" t="n">
-        <v>97.6187610347945</v>
+        <v>92.59489254081609</v>
       </c>
       <c r="E10" t="n">
-        <v>43.84608835461794</v>
+        <v>42.53136058630704</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.4405496120452881</v>
+        <v>0.5450255870819092</v>
       </c>
       <c r="I10" t="n">
         <v>48192</v>
@@ -806,19 +806,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-2.291189939668012</v>
+        <v>-0.03950752495290044</v>
       </c>
       <c r="B11" t="n">
-        <v>158.2867711645409</v>
+        <v>28.36241018978324</v>
       </c>
       <c r="C11" t="n">
-        <v>29763.6052745423</v>
+        <v>9683.816140855051</v>
       </c>
       <c r="D11" t="n">
-        <v>172.521318319048</v>
+        <v>98.40638262254664</v>
       </c>
       <c r="E11" t="n">
-        <v>129.2158105365643</v>
+        <v>14.33766091381153</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -831,30 +831,30 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.3730933666229248</v>
+        <v>1.763675451278687</v>
       </c>
       <c r="I11" t="n">
-        <v>48192</v>
+        <v>48168</v>
       </c>
       <c r="J11" t="n">
-        <v>744</v>
+        <v>720</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.01214206915473026</v>
+        <v>-0.07616446856212478</v>
       </c>
       <c r="B12" t="n">
-        <v>54.21270046584622</v>
+        <v>62.15189473505158</v>
       </c>
       <c r="C12" t="n">
-        <v>9153.223478532705</v>
+        <v>9732.204776975479</v>
       </c>
       <c r="D12" t="n">
-        <v>95.67248025703476</v>
+        <v>98.65193752266337</v>
       </c>
       <c r="E12" t="n">
-        <v>38.85275215102043</v>
+        <v>45.88845605681207</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1097.96142077446</v>
+        <v>1162.552569627762</v>
       </c>
       <c r="I12" t="n">
         <v>48192</v>
@@ -878,19 +878,19 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-2.291189939668012</v>
+        <v>-0.03950912770797221</v>
       </c>
       <c r="B13" t="n">
-        <v>158.2867711645409</v>
+        <v>28.36236785095883</v>
       </c>
       <c r="C13" t="n">
-        <v>29763.6052745423</v>
+        <v>9683.831071757486</v>
       </c>
       <c r="D13" t="n">
-        <v>172.521318319048</v>
+        <v>98.40645848600327</v>
       </c>
       <c r="E13" t="n">
-        <v>129.2158105365643</v>
+        <v>14.33763343663002</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -903,30 +903,30 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.3659670352935791</v>
+        <v>1.118541479110718</v>
       </c>
       <c r="I13" t="n">
-        <v>48192</v>
+        <v>48168</v>
       </c>
       <c r="J13" t="n">
-        <v>744</v>
+        <v>720</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-2.576035132468065</v>
+        <v>-1.221218528660495</v>
       </c>
       <c r="B14" t="n">
-        <v>167.0081149559878</v>
+        <v>117.2941585693608</v>
       </c>
       <c r="C14" t="n">
-        <v>32339.57932595388</v>
+        <v>20087.4069037229</v>
       </c>
       <c r="D14" t="n">
-        <v>179.8320864750056</v>
+        <v>141.7300494028098</v>
       </c>
       <c r="E14" t="n">
-        <v>136.6869763235567</v>
+        <v>92.80425547973229</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.03354763984680176</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>48192</v>
@@ -950,19 +950,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-2.576035132468065</v>
+        <v>-1.221218528660495</v>
       </c>
       <c r="B15" t="n">
-        <v>167.0081149559878</v>
+        <v>117.2941585693608</v>
       </c>
       <c r="C15" t="n">
-        <v>32339.57932595388</v>
+        <v>20087.4069037229</v>
       </c>
       <c r="D15" t="n">
-        <v>179.8320864750056</v>
+        <v>141.7300494028098</v>
       </c>
       <c r="E15" t="n">
-        <v>136.6869763235567</v>
+        <v>92.80425547973229</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.03468823432922363</v>
+        <v>0.01565074920654297</v>
       </c>
       <c r="I15" t="n">
         <v>48192</v>
@@ -986,19 +986,19 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-2.576035132468065</v>
+        <v>-1.221218528660495</v>
       </c>
       <c r="B16" t="n">
-        <v>167.0081149559878</v>
+        <v>117.2941585693608</v>
       </c>
       <c r="C16" t="n">
-        <v>32339.57932595388</v>
+        <v>20087.4069037229</v>
       </c>
       <c r="D16" t="n">
-        <v>179.8320864750056</v>
+        <v>141.7300494028098</v>
       </c>
       <c r="E16" t="n">
-        <v>136.6869763235567</v>
+        <v>92.80425547973229</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.03478646278381348</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>48192</v>
@@ -1022,19 +1022,19 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.09302392833861517</v>
+        <v>-0.5797846482342093</v>
       </c>
       <c r="B17" t="n">
-        <v>64.06928518233761</v>
+        <v>94.84817002409248</v>
       </c>
       <c r="C17" t="n">
-        <v>9884.671913521266</v>
+        <v>14286.6524116708</v>
       </c>
       <c r="D17" t="n">
-        <v>99.42168733994242</v>
+        <v>119.5267853314511</v>
       </c>
       <c r="E17" t="n">
-        <v>45.76518374271319</v>
+        <v>73.86612884149319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1047,156 +1047,12 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.3607857227325439</v>
+        <v>0.2396271228790283</v>
       </c>
       <c r="I17" t="n">
         <v>48192</v>
       </c>
       <c r="J17" t="n">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>-0.03280322929103341</v>
-      </c>
-      <c r="B18" t="n">
-        <v>27.87891665433511</v>
-      </c>
-      <c r="C18" t="n">
-        <v>9340.070979310211</v>
-      </c>
-      <c r="D18" t="n">
-        <v>96.64404264780219</v>
-      </c>
-      <c r="E18" t="n">
-        <v>11.91526079089405</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>v9_date_range_all</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Decision Tree</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>0.2105541229248047</v>
-      </c>
-      <c r="I18" t="n">
-        <v>48192</v>
-      </c>
-      <c r="J18" t="n">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>-2.291189939668012</v>
-      </c>
-      <c r="B19" t="n">
-        <v>158.2867711645409</v>
-      </c>
-      <c r="C19" t="n">
-        <v>29763.6052745423</v>
-      </c>
-      <c r="D19" t="n">
-        <v>172.521318319048</v>
-      </c>
-      <c r="E19" t="n">
-        <v>129.2158105365643</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>v9_date_range_all_lags</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Lasso</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>0.3766143321990967</v>
-      </c>
-      <c r="I19" t="n">
-        <v>48192</v>
-      </c>
-      <c r="J19" t="n">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>-3.350947531108349</v>
-      </c>
-      <c r="B20" t="n">
-        <v>112.2089919354839</v>
-      </c>
-      <c r="C20" t="n">
-        <v>39347.43580895125</v>
-      </c>
-      <c r="D20" t="n">
-        <v>198.3618809372185</v>
-      </c>
-      <c r="E20" t="n">
-        <v>85.435361693522</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>v10_date_range_no_solar</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Decision Tree</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>0.6520884037017822</v>
-      </c>
-      <c r="I20" t="n">
-        <v>48192</v>
-      </c>
-      <c r="J20" t="n">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>-2.291189939668012</v>
-      </c>
-      <c r="B21" t="n">
-        <v>158.2867711645409</v>
-      </c>
-      <c r="C21" t="n">
-        <v>29763.6052745423</v>
-      </c>
-      <c r="D21" t="n">
-        <v>172.521318319048</v>
-      </c>
-      <c r="E21" t="n">
-        <v>129.2158105365643</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>v10_date_range_no_solar_lags</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Lasso</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>0.4014136791229248</v>
-      </c>
-      <c r="I21" t="n">
-        <v>48192</v>
-      </c>
-      <c r="J21" t="n">
         <v>744</v>
       </c>
     </row>
